--- a/artfynd/A 41906-2026 artfynd.xlsx
+++ b/artfynd/A 41906-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325687</v>
       </c>
       <c r="B2" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137325688</v>
       </c>
       <c r="B3" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41906-2026 artfynd.xlsx
+++ b/artfynd/A 41906-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325687</v>
       </c>
       <c r="B2" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137325688</v>
       </c>
       <c r="B3" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41906-2026 artfynd.xlsx
+++ b/artfynd/A 41906-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325687</v>
       </c>
       <c r="B2" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137325688</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41906-2026 artfynd.xlsx
+++ b/artfynd/A 41906-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325687</v>
       </c>
       <c r="B2" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137325688</v>
       </c>
       <c r="B3" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41906-2026 artfynd.xlsx
+++ b/artfynd/A 41906-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325687</v>
       </c>
       <c r="B2" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137325688</v>
       </c>
       <c r="B3" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41906-2026 artfynd.xlsx
+++ b/artfynd/A 41906-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325687</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137325688</v>
       </c>
       <c r="B3" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41906-2026 artfynd.xlsx
+++ b/artfynd/A 41906-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325687</v>
       </c>
       <c r="B2" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137325688</v>
       </c>
       <c r="B3" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
